--- a/experiment/ELAN_bestx3/Test/results-Set5/Set5.xlsx
+++ b/experiment/ELAN_bestx3/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.55</v>
+        <v>35.69</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8464</v>
+        <v>0.9305</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.49</v>
+        <v>37.91</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8759</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.87</v>
+        <v>31.33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7958</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.37</v>
+        <v>34.09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7531</v>
+        <v>0.8362000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.71</v>
+        <v>33.06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8384</v>
+        <v>0.9462</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.4</v>
+        <v>34.42</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8219</v>
+        <v>0.9268</v>
       </c>
     </row>
   </sheetData>
